--- a/base_prov_co/farmatodo/farmatodo_abbott_2026_10_15.xlsx
+++ b/base_prov_co/farmatodo/farmatodo_abbott_2026_10_15.xlsx
@@ -552,7 +552,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Ensure Advance Vainilla Con Proteína + Hmb Polvo X 850 Gr</t>
+        </is>
+      </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
           <t>8427030008608</t>
@@ -574,22 +578,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+        <v>614</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Ensure está formulado para adultos que requieren recuperar su estado nutricional al pasar por una condición médica. Está específicamente diseñado para proveerlos nutrientes necesarios para apoyar una correcta alimentación. Contiene una combinación de macro y micronutrientes (28 vitaminas y minerales, proteínas, fibras, carbohidratos y ácidos grasos). Ademas, aporta fibra (FOS) que actúa a nivel intestinal, está formulado con antioxidantes y vitaminas (C,E y Selenio) y no contiene grasas trans.
+Contiene HMB (beta-hidroxi-beta-metilbutirato), un nutriente que ayuda a preservar y reconstruir la masa muscular.</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/tDemCES5thCtaZ8q_8lDsQDj4YU3s7M3vZk0Xkt2WAXE5KfPOXfc06PHf2vXbOJOP9kgK-16_QBY--Qcx-Xq093NeIYxrMWqdIgGVqosYDWUMibU0biw-Vfx41xitg=s360-rw</t>
+        </is>
+      </c>
       <c r="Q2" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/1050596-ensure-advance-vainilla</t>
@@ -597,7 +618,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -612,7 +633,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ensure Advance Vainilla Con Proteina + Hmb Liquido Botella X 220 Ml</t>
+        </is>
+      </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>8710428018670</t>
@@ -634,22 +659,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
+        <v>114</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Contiene HMB (beta-hidroxi-beta-metilbutirato), un nutriente que ayuda a preservar y reconstruir la masa muscular.</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/0_AI5tk75G6mK4visr8C1FpDG7ovasazCaIpjw7XBtbdSgnoixtNtF6zPxepDfXFeX5zvXB7StU6QwTqO9rGZw5kf4Dui37KmBq7GH76DZOw_4Z1pw=s360-rw</t>
+        </is>
+      </c>
       <c r="Q3" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/232300088-ensure-advance-rpb-sabor</t>
@@ -657,7 +698,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -672,7 +713,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ensure Advance Vainilla Con Proteína + Hmb Liquido X 220 Ml Caja X 6 Botellas</t>
+        </is>
+      </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
           <t>7703186033031</t>
@@ -694,22 +739,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
+        <v>499</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Ensure Advance es ideal para adultos que requieran mantener o recuperar su masa muscular perdida por una condición de salud, y volver a llevar un estilo de vida activo.Formulado con CaHMB y proteína para los músculos, así como 28 vitaminas y minerales, incluyendo calcio y vitamina D, que apoyan la vitalidad fuerza y energía. También contiene omega 3 y 6 y no contiene grasas trans.
+Contiene HMB (beta-hidroxi-beta-metilbutirato), un nutriente que ayuda a preservar y reconstruir la masa muscular.</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/-ebsasjD6ZLLvc2w268NgcYskLHOuBTH-YkwBtYwemNcNmg5YJGZ_3lzXlW8FduAAc46PnP2b5wmWHr3wpTn6mQnAvEYddLygQPK28EQxG_u7Nsr=s360-rw</t>
+        </is>
+      </c>
       <c r="Q4" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/233000052-ensure-advance-rpb-sabor</t>
@@ -717,7 +779,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -732,7 +794,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ensure Advance Vainilla Con Proteina + Hmb Lata X 400 Gr</t>
+        </is>
+      </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
           <t>8427030008592</t>
@@ -754,22 +820,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
+        <v>499</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Ensure Advance es ideal para adultos que requieran mantener o recuperar su masa muscular perdida por una condición de salud, y volver a llevar un estilo de vida activo.Formulado con CaHMB y proteína para los músculos, así como 28 vitaminas y minerales, incluyendo calcio y vitamina D, que apoyan la vitalidad fuerza y energía. También contiene omega 3 y 6 y no contiene grasas trans.
+Contiene HMB (beta-hidroxi-beta-metilbutirato), un nutriente que ayuda a preservar y reconstruir la masa muscular.</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/4O8yfN1jecVWayzbzcfpkxK5eZpNAbXCh6UF0G53hwGa51C_vGWFVbtUxhhVMjGTCxoMw-I8XEiX5qpNlA-u_iTst3aK3aVyek7RrhTSGJxZ_rU-nQ=s360-rw</t>
+        </is>
+      </c>
       <c r="Q5" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/1043564-ensure-advance-vainilla</t>
@@ -777,7 +860,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -792,7 +875,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ensure Advance Fresa Con Proteina + Hmb Liquido X 220 Ml</t>
+        </is>
+      </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
           <t>8710428018717</t>
@@ -814,22 +901,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+        <v>499</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Ensure Advance es ideal para adultos que requieran mantener o recuperar su masa muscular perdida por una condición de salud, y volver a llevar un estilo de vida activo.Formulado con CaHMB y proteína para los músculos, así como 28 vitaminas y minerales, incluyendo calcio y vitamina D, que apoyan la vitalidad fuerza y energía. También contiene omega 3 y 6 y no contiene grasas trans.
+Contiene HMB (beta-hidroxi-beta-metilbutirato), un nutriente que ayuda a preservar y reconstruir la masa muscular.</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/qfwAGNKzLRmYYr66fUVczRavtA-bZ-pSaOUcCYI5PYLPNxR8RZApYl4fKn6j_qS_k0B-osiwTjq1KLLtRb5NuYdcwvx5im4jE7_xWPAfUDiM1KeT=s360-rw</t>
+        </is>
+      </c>
       <c r="Q6" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/232350085-ensure-advance-rpb-sabor</t>
@@ -837,7 +941,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -852,7 +956,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ensure Advance Fresa Con Proteina + Hmb Tarro X 850 Gr</t>
+        </is>
+      </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
           <t>8710428013859</t>
@@ -874,22 +982,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
+        <v>614</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Ensure está formulado para adultos que requieren recuperar su estado nutricional al pasar por una condición médica. Está específicamente diseñado para proveerlos nutrientes necesarios para apoyar una correcta alimentación. Contiene una combinación de macro y micronutrientes (28 vitaminas y minerales, proteínas, fibras, carbohidratos y ácidos grasos). Ademas, aporta fibra (FOS) que actúa a nivel intestinal, está formulado con antioxidantes y vitaminas (C,E y Selenio) y no contiene grasas trans.
+Contiene HMB (beta-hidroxi-beta-metilbutirato), un nutriente que ayuda a preservar y reconstruir la masa muscular.</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/mOsezleQcN_oqPJXGh4eGTTmRNnx9SsbiVMpjzn2cqcLXe9Qsxl3FJIxNZXjebqUzeorFvmiiC22-1TRImgkWHG6ZamrvGPi6ZSmmzC6w8MKGvWp=s360-rw</t>
+        </is>
+      </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/106461753-ensure-advance-fresa</t>
@@ -897,7 +1022,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -912,7 +1037,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ensure Advance 400 Gr + Ensure Advance Líquido Sabor Vainilla Oferta X 2 Und</t>
+        </is>
+      </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
           <t>7703186998262</t>
@@ -937,19 +1066,27 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
+        <v>616</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Complemento nutricional para adultos, con Hmb, vitaminas y minerales. Para personas que requieran recuperar o mantener su masa corporal magra. Alimento en polvo para propósitos médicos especiales, polimérico, a base de maltodextrina, proteína, Hmb, vitaminas y minerales para adultos y adultos mayores que requieren recuperar mantener su masa corporal magra. Modo de uso Instrucciones de uso para preparar una porción de 230 ml, vierta 190ml de agua fría o a temperatura ambiente en un vaso y adicione gradualmente 6 mededas rasas cuchara medidora incluida ó 54.1g de Ensure Advance polvo. Agite hasta disolver el po</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/Z0iklNq6OEbHkmkLoUaywrL_nnphhsMg9PDboJQk-wdg22F5akPWJEWPaZxD26T6Ud7Tn1UFrWOYZG-mc275jk7X0_AtdtR4GgM4m65MFqa9WVI=s360-rw</t>
+        </is>
+      </c>
       <c r="Q8" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/238000246-ensure-advance-400-gr-ensure-advance-liquido-sabor-vainilla-oferta-x-2-und</t>
@@ -957,7 +1094,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -972,7 +1109,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ensure Advance Chocolate Con Proteina + Hmb Liquido Frasco X 220 Ml</t>
+        </is>
+      </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
           <t>8710428018694</t>
@@ -994,22 +1135,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
+        <v>499</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Ensure Advance es ideal para adultos que requieran mantener o recuperar su masa muscular perdida por una condición de salud, y volver a llevar un estilo de vida activo.Formulado con CaHMB y proteína para los músculos, así como 28 vitaminas y minerales, incluyendo calcio y vitamina D, que apoyan la vitalidad fuerza y energía. También contiene omega 3 y 6 y no contiene grasas trans.
+Contiene HMB (beta-hidroxi-beta-metilbutirato), un nutriente que ayuda a preservar y reconstruir la masa muscular.</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/J5du7T8gJIu4fd6qPsXHQIDMRSHLT6BfyMoXdmjmwTrlqyqnWNEDDSZo_1m7vgyR3kLNhZWxsBzNfiWPA9kXDXzLLXx_egIbqKeVkLIZFdrbtV4=s360-rw</t>
+        </is>
+      </c>
       <c r="Q9" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/232350077-ensure-advance-rpb-sabor</t>
@@ -1017,7 +1175,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1190,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ensure Sabor Vainilla Con Proteína Lata X 400 Gr</t>
+        </is>
+      </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
           <t>8427030003153</t>
@@ -1054,22 +1216,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
+        <v>620</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Ensure está formulado para adultos que requieren recuperar su estado nutricional al pasar por una condición médica. Está específicamente diseñado para proveerlos nutrientes necesarios para apoyar una correcta alimentación. Contiene una combinación de macro y micronutrientes (28 vitaminas y minerales, proteínas, fibras, carbohidratos y ácidos grasos). Ademas, aporta fibra (FOS) que actúa a nivel intestinal, está formulado con antioxidantes y vitaminas (C,E y Selenio) y no contiene grasas trans.
+Nutrición especializada para adultos: contiene proteína, vitaminas y minerales para complementar tu alimentación diaria.</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/KpUwD44x79aXzeo5l-00O1cOZhoLv9CA-3g4EVDOlFNfqzfDrlZM0hfH0iQGJgdii_qfdORQUxBpXGVGbxZwL2UAZjo8wGFfK1Joae-PBUp05Ac=s360-rw</t>
+        </is>
+      </c>
       <c r="Q10" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/1017009-ensure-vainilla-x400g</t>
@@ -1077,7 +1256,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1271,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ensure Sabor Vainilla Liquido Botella X 220 Gr</t>
+        </is>
+      </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
           <t>8710428019561</t>
@@ -1114,22 +1297,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
+        <v>620</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Ensure está formulado para adultos que requieren recuperar su estado nutricional al pasar por una condición médica. Está específicamente diseñado para proveerlos nutrientes necesarios para apoyar una correcta alimentación. Contiene una combinación de macro y micronutrientes (28 vitaminas y minerales, proteínas, fibras, carbohidratos y ácidos grasos). Ademas, aporta fibra (FOS) que actúa a nivel intestinal, está formulado con antioxidantes y vitaminas (C,E y Selenio) y no contiene grasas trans.
+Nutrición especializada para adultos: contiene proteína, vitaminas y minerales para complementar tu alimentación diaria.</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/oy7geihxMLCI2QLrtp_crhdqGG2f-sim7q6Aj7-PuLUnEIPfxcLmSXDW7SoLiXXnX43Hu2tjvfwsV94x5oIoR9SD1cp4k3-9yQLf85iXNRqYsfYH=s360-rw</t>
+        </is>
+      </c>
       <c r="Q11" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/237850038-ensure-sabor-vainilla</t>
@@ -1137,7 +1337,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1352,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ensure Clinical Sabor Vainilla Liquido Botella X 220 Ml</t>
+        </is>
+      </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
           <t>7703186031433</t>
@@ -1174,22 +1378,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
+        <v>531</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Ensure Clinical es un alimento para propositos medicos especialespara adultosque presenten sarcopenia o caquexia asociada a desnutrición proteico-calórica moderada o severa asociada a una condición médica. Aporta 1,5 Kcal/ml y está formulado con HMB, 28 vitaminas y minerales para apoyar su alimentación en adultos con una perdida mayor en masa muscular y que no logran suplir sus requerimientos nutricionales con una alimentación normal o modificada.
+Contiene HMB, calcio y vitamina D3, nutrientes clave para el soporte muscular.</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/Rpe_YcH6Diwwn4aLCOo5MfLnsiNUqjo4cHbRMXBFgYzUDYzfJRe5aS5Uv8-ImUIv7jFlNcuXIlX3-ebfvuIY-AYRqDPhG1yTAofRGlUBn49ymdQ=s360-rw</t>
+        </is>
+      </c>
       <c r="Q12" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/211200192-ensure-clinical-rpb-x-220-ml</t>
@@ -1197,7 +1418,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1433,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ensure Advance Café Con Proteína + Hmb Líquido Botella X 220 Ml</t>
+        </is>
+      </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
           <t>8710428018861</t>
@@ -1234,22 +1459,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
+        <v>520</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Ensure Advance es un alimento para propositos medicos especiales, dirigido adultos que requieran mantener o recuperar su masa muscular perdida por una condición de salud, y volver a llevar un estilo de vida activo.Formulado con CaHMB y proteína para apoyar los músculos, así como 28 vitaminas y minerales, que apoyan la vitalidad fuerza y energía. También contiene omega 3 y 6 y no contiene grasas trans.
+Contiene HMB (beta-hidroxi-beta-metilbutirato), un nutriente que ayuda a preservar y reconstruir la masa muscular.</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/n6KuqQOumNI_aZAvmVgS4ExjWYWtBIfAwxlzY2VQN4M0_7ZczRWXVDuRNM94gAuacn4rVK_fk4C2K8WTnSchbvbQVN_PrG72MriB0PO6iXy7QEYe7g=s360-rw</t>
+        </is>
+      </c>
       <c r="Q13" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/237850046-ensure-advance-sabor</t>
@@ -1257,7 +1499,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1514,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ensure Advance Café Con Proteina + Hmb Lata X 400 Gr</t>
+        </is>
+      </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
           <t>7703186341334</t>
@@ -1297,19 +1543,28 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
+        <v>525</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Ensure Advance Cafe es un alimento para propositos medicos especiales, dirigido adultos que requieran mantener o recuperar su masa muscular perdida por una condición de salud, y volver a llevar un estilo de vida activo.Formulado con CaHMB y proteína para apoyar los músculos, así como 28 vitaminas y minerales, que apoyan la vitalidad fuerza y energía. También contiene omega 3 y 6 y no contiene grasas trans.
+Contiene HMB (beta-hidroxi-beta-metilbutirato), un nutriente que ayuda a preservar y reconstruir la masa muscular.</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/GBWY1wB9vq2AiHrj3mACrgs0RYERxnfxNlK0BsnVDyjg2XAW0EztmNXEC1B1ss4YEJGkU9CVS1f-WblimX37J7BRPo81PGRRE9dC9wtQdl8poSX2iQ=s360-rw</t>
+        </is>
+      </c>
       <c r="Q14" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/239100214-ensure-advance-cafe-lata-x-400-gr</t>
@@ -1317,7 +1572,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -1332,7 +1587,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ensure Advance Chocolate Con Proteina + Hmb Tarro X 400 Gr</t>
+        </is>
+      </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
           <t>8710428011848</t>
@@ -1354,22 +1613,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
+        <v>499</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Ensure Advance es ideal para adultos que requieran mantener o recuperar su masa muscular perdida por una condición de salud, y volver a llevar un estilo de vida activo.Formulado con CaHMB y proteína para los músculos, así como 28 vitaminas y minerales, incluyendo calcio y vitamina D, que apoyan la vitalidad fuerza y energía. También contiene omega 3 y 6 y no contiene grasas trans.
+Contiene HMB (beta-hidroxi-beta-metilbutirato), un nutriente que ayuda a preservar y reconstruir la masa muscular.</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/CCGB9PI4tbNtuMBk8YvmZT2kFUBvcpBG22iTE-ssQ76BuP_cnSw7x0YmTZa63Zro9YWN4mlUdsCE3lrSGpFzqIyjojcPDzsqPeejD2Ju4vbOJK8=s360-rw</t>
+        </is>
+      </c>
       <c r="Q15" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/206650228-ensure-advance-chocolate</t>
@@ -1377,7 +1653,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1668,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ensure Plus Hn Liquido Botella X 220 Ml</t>
+        </is>
+      </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
           <t>8710428017987</t>
@@ -1414,22 +1694,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
+        <v>595</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Ensure Plus HN alimento para propositos medicos especiales, diseñada para adultos que están en riesgo nutricional o que experimentan pérdida de peso involuntaria asociada a una condición de salud. Es una fórmula nutricional alta en calorías (1.5 kcal/ml), que contiene una combinación de proteínas, 28 vitaminas y minerales, y un balance adecuado de ácidos grasos omega 3 y omega 6. Es ideal para ayudarte a mejorar tu estado nutricional y contribuir a una ganancia de masa corporal adecuada.
+Aporta 14?g de proteína por porción (220?ml), ideal para apoyar el mantenimiento de la masa muscular.</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/w-qOAc0LGQcHntzRhdezMut9K7oLHg0ibNWBmLbI8ZBRtPvq1PQyTGyP4Ak6tqtowv_sZIOIPeajL_XO0ujr5-QQl2EmP-kcPZ6TsRXEIWmxJZw2=s360-rw</t>
+        </is>
+      </c>
       <c r="Q16" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/229350210-ensure-plus-rpb-hn-x220ml</t>
@@ -1437,7 +1734,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1749,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Fórmula Especializada Pulmocare Vainilla Líquido Tarro X 237 Ml</t>
+        </is>
+      </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
           <t>7703186069917</t>
@@ -1474,22 +1775,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
+        <v>467</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Pulmocare Vainilla 237 mL es un alimento para propósitos médicos especiales formulado para personas con enfermedades respiratorias crónicas como EPOC, insuficiencia respiratoria, fibrosis pulmonar, fibrosis quística o enfisema pulmonar. Su fórmula hipercalórica y nutricionalmente completa ayuda a cubrir las necesidades energéticas y nutricionales cuando la alimentación habitual no es suficiente
+Nutrición especializada para personas con enfermedades respiratorias</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/gqt7zmQ4sfoUV0260qBBFSNzzSWul4VJHk1hh49a8G4_wI0V3pcOCYSzj9Sgamj1jhnr30lT6gp7onwgePwi25VVhSS3sBhrloz404SVhxbirEcH=s360-rw</t>
+        </is>
+      </c>
       <c r="Q17" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/1015930-pulmocare-x237ml</t>
@@ -1497,7 +1815,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1830,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Fórmula Especializada Prosure Vainilla Liquido Frasco X 220 Ml</t>
+        </is>
+      </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
           <t>8710428022790</t>
@@ -1534,22 +1856,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
+        <v>444</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>ProSure Vainilla 220 mL es un alimento para propósitos médicos especiales, formulado para brindar soporte nutricional a adolescentes y adultos con desnutrición asociada a enfermedades oncológicas, pérdida involuntaria de peso o caquexia. Su fórmula hiperproteica contiene EPA y FOS, nutrientes que ayudan a complementar los requerimientos nutricionales cuando la alimentación habitual no es suficiente.
+Contiene 14,5 g de proteína por porción.</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/ym8TG6WxxQTd-s0PTjxGzxRf0glY1tk-FA94Lvt_ADp-5e73guXH4HWcU-xgtrx5Gg_B7hGJKboF5_NK5W4u_zRC7YBi8T6D6pjRze6dqMLcRE6A9w=s360-rw</t>
+        </is>
+      </c>
       <c r="Q18" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/211200379-alimento-liquido-prosure</t>
@@ -1557,7 +1896,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -1572,7 +1911,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Fórmula Para Diabetes Glucerna Sabor Vainilla Lata X 850 Gr</t>
+        </is>
+      </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
           <t>8427030008943</t>
@@ -1594,22 +1937,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
+        <v>584</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Glucerna te ayuda a nivelar tus niveles de azúcar en 4 semanas gracias a su fórmula única con bajo índice glicémico, carbohidratos de lenta digestión y m-inositol compuestoque ayuda a respaldar el metabolismo, los nivenes de glucosa y la sensibilidad a la insulina. Glucerna es nutrición especializada para personas con diabetes tipo 2 o hiperglicemia, es alta en proteina, sin azucares añadidos y fuente de 28 vitaminas y minerales. Glucerna actúa desde el primer día.
+Aporta 11,1 g de proteína y 8,6 g de fibra por porción. Apoya el control glucémico y el funcionamiento digestivo.</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/Z00lSvFocl-r2Pd-UqCh5gBJoipeh7nUrTDJkZlsyo99fI3Zfu_KZgQIZS1htLJ-5KmddAvAmNJbgBsqTl0rozO7kztszsOM6XVAJFNdyj89JRAlNQ=s360-rw</t>
+        </is>
+      </c>
       <c r="Q19" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/283000464-glucerna-vainilla-850</t>
@@ -1617,7 +1977,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1992,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Fórmula Para Diabetes Glucerna Líquido Vainilla Frasco X 237 Ml</t>
+        </is>
+      </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
           <t>7703186030283</t>
@@ -1654,22 +2018,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
+        <v>581</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Glucerna te ayuda a nivelar tus niveles de azúcar en 4 semanas gracias a su fórmula única con bajo índice glicémico, carbohidratos de lenta digestión y m-inositol compuestoque ayuda a respaldar el metabolismo, los nivenes de glucosa y la sensibilidad a la insulina. Glucerna es nutrición especializada para personas con diabetes tipo 2 o hiperglicemia, es alta en proteina, sin azucares añadidos y fuente de 28 vitaminas y minerales. Glucerna actúa desde el primer día.
+Contiene 11 g de proteína y 8,8 g de fibra por porción para apoyar la saciedad, el metabolismo y la digestión.</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/COZtnpSO9XE0WddQprUHc7J0hBf8xSvAQFrlFmrEdDiSlVal0WcGnPEIVj273CWcWX4QvKnzP0K3i7NOS_yNk-SZ8lzGxpN3J48-t5Zmb0gPyu90=s360-rw</t>
+        </is>
+      </c>
       <c r="Q20" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/1050402-glucerna-vainilla</t>
@@ -1677,7 +2058,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -1692,7 +2073,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Glucerna Vainilla Oferta 850gr + 400gr X 2 Latas</t>
+        </is>
+      </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
           <t>7703186499844</t>
@@ -1717,19 +2102,27 @@
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
+        <v>610</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Oferta Glucerna Vainilla 850 más Glucerna Vainilla 400gr con el 21 de descuento. Alimento con propósito medicos especiales con una mezcla de carbohidratos de digestión lenta, para personas con diabetes o hiperglicemia. Alimento en polvo para propósitos médicos especiales, polimérico e hiperproteico, a base de una mezcla de carbohidratos de digestión lenta para intervención nutricional por vía oral o sonda a adultos con diabetes tipo 2 o hiperglicemia. Modo de uso ? Oral / Sonda ? Administrar sólo bajo supervisión médica ? Para administración por sonda siga las recomendaciones del profesional de la salud</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/udy8wB0eEbibuq-V1f5T8tTlDVLNK6EW8vngZ5ZLqoj-yxKVfw79D3euSbLctoEVWZCzhETjHMVxlijTCDF_Su5LsI-ibZZWLJA68450FIgkn11R=s360-rw</t>
+        </is>
+      </c>
       <c r="Q21" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/243900265-glucerna-vainilla-oferta-850gr-400gr-x-2-latas</t>
@@ -1737,7 +2130,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -1752,7 +2145,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Fórmula Para Diabetes Glucerna Sabor Vainilla Liquido Caja X 6 Botellas De 237ml C/u</t>
+        </is>
+      </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
           <t>7703186032737</t>
@@ -1774,22 +2171,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
+        <v>581</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Glucerna te ayuda a nivelar tus niveles de azúcar en 4 semanas gracias a su fórmula única con bajo índice glicémico, carbohidratos de lenta digestión y m-inositol compuestoque ayuda a respaldar el metabolismo, los nivenes de glucosa y la sensibilidad a la insulina. Glucerna es nutrición especializada para personas con diabetes tipo 2 o hiperglicemia, es alta en proteina, sin azucares añadidos y fuente de 28 vitaminas y minerales. Glucerna actúa desde el primer día.
+Contiene 11 g de proteína y 8,8 g de fibra por porción para apoyar la saciedad, el metabolismo y la digestión.</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/0ZKOaxMHwV9DV_iWyZBdxokzmnzGOwAG7v8LjVbgI3ifIFzssQewaaZJRfHO2o9H1Lych2AX9iyvu80Y7tZD157Nn9eXECVLQuIkQIfY-o4k2u37rg=s360-rw</t>
+        </is>
+      </c>
       <c r="Q22" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/107611792-oft-glucerna-vainilla</t>
@@ -1797,7 +2211,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -1812,7 +2226,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Glucerna Líquido Sabor Vainilla Y Fresa Pack X 8 Und</t>
+        </is>
+      </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
           <t>7703186190376</t>
@@ -1837,19 +2255,27 @@
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
+        <v>469</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Glucerna te ayuda a nivelar tus niveles de azúcar en 4 semanas gracias a su fórmula única con bajo índice glicémico, carbohidratos de lenta digestión y m-inositol compuestoque ayuda a respaldar el metabolismo, los nivenes de glucosa y la sensibilidad a la insulina. Glucerna es nutrición especializada para personas con diabetes tipo 2 o hiperglicemia, es alta en proteina, sin azucares añadidos y fuente de 28 vitaminas y minerales. Glucerna actúa desde el primer día.</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/Jv10LxuFpvuVEStC7JBjbjw-yQFMctnqzGzz7J5OoJG5RdoXnL5x1TBiJaorzZaWYcUpzk2AasTrFWkm_cM4UakZVsDvLAUFPvMRyPtVpb0BwBE2=s360-rw</t>
+        </is>
+      </c>
       <c r="Q23" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/239150289-glucerna-liquido-sabor-vainilla-y-fresa-pack-x-8-und</t>
@@ -1857,7 +2283,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -1872,7 +2298,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Glucerna Fresa Líquido X 237 Ml</t>
+        </is>
+      </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
           <t>7703186031525</t>
@@ -1894,22 +2324,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
+        <v>581</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Glucerna te ayuda a nivelar tus niveles de azúcar en 4 semanas gracias a su fórmula única con bajo índice glicémico, carbohidratos de lenta digestión y m-inositol compuestoque ayuda a respaldar el metabolismo, los nivenes de glucosa y la sensibilidad a la insulina. Glucerna es nutrición especializada para personas con diabetes tipo 2 o hiperglicemia, es alta en proteina, sin azucares añadidos y fuente de 28 vitaminas y minerales. Glucerna actúa desde el primer día.
+Contiene 11 g de proteína y 8,8 g de fibra por porción para apoyar la saciedad, el metabolismo y la digestión.</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/xlhbaatSuzOalVx6s4VHyNONxxU204xticq13epM4V59WUap5ZYrCaEQ5gzHE3ue6dwvS0om5NmKapg-VXMsx1tk8g7FVMlie5TM7-YAY_g4mwYa=s360-rw</t>
+        </is>
+      </c>
       <c r="Q24" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/1052904-glucerna-fresa</t>
@@ -1917,7 +2364,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -1932,7 +2379,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Glucerna Vainilla Polvo X 400 Gr</t>
+        </is>
+      </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
           <t>8427030008936</t>
@@ -1954,22 +2405,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
+        <v>469</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Glucerna te ayuda a nivelar tus niveles de azúcar en 4 semanas gracias a su fórmula única con bajo índice glicémico, carbohidratos de lenta digestión y m-inositol compuestoque ayuda a respaldar el metabolismo, los nivenes de glucosa y la sensibilidad a la insulina. Glucerna es nutrición especializada para personas con diabetes tipo 2 o hiperglicemia, es alta en proteina, sin azucares añadidos y fuente de 28 vitaminas y minerales. Glucerna actúa desde el primer día.</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/hkw61HR6BY9z9RdQGIIGIu6t7VXAWAvwv8KrF5kbf0kjlAQbIp_Y-7EBgiKpvLq0_iJhiAw36kyml2RIYw110MN5CJbnNMJDRZGH93ZzR9Tt0oE=s360-rw</t>
+        </is>
+      </c>
       <c r="Q25" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/1026565-glucerna-sr-vainilla</t>
@@ -1977,7 +2444,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -1992,7 +2459,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Fórmula Para Diabetes Glucerna Sabor Capuchino Lata X 400 Gr</t>
+        </is>
+      </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
           <t>8427030009346</t>
@@ -2017,19 +2488,28 @@
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
+        <v>584</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Glucerna te ayuda a nivelar tus niveles de azúcar en 4 semanas gracias a su fórmula única con bajo índice glicémico, carbohidratos de lenta digestión y m-inositol compuestoque ayuda a respaldar el metabolismo, los nivenes de glucosa y la sensibilidad a la insulina. Glucerna es nutrición especializada para personas con diabetes tipo 2 o hiperglicemia, es alta en proteina, sin azucares añadidos y fuente de 28 vitaminas y minerales. Glucerna actúa desde el primer día.
+Aporta 11,1 g de proteína y 8,6 g de fibra por porción. Apoya el control glucémico y el funcionamiento digestivo.</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/u2jXytYeaQCd2NCItOk4IwUvpm8dpAkxK3YBnuoBeA6--QU-kMDJg-aUgMTJwI9nC4_0uE_g0lT9-jUoAJYkDQp8F3_r0KZelNt7D-iYUAeas6gz=s360-rw</t>
+        </is>
+      </c>
       <c r="Q26" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/243950238-glucerna-abbott-sabor-capuchino-lata-x-400-gr</t>
@@ -2037,7 +2517,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2532,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Fórmula Para Diabetes Glucerna Líquido Sabor Vainilla Frasco X 220 Ml</t>
+        </is>
+      </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
           <t>8710428024299</t>
@@ -2077,19 +2561,28 @@
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
+        <v>581</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Glucerna te ayuda a nivelar tus niveles de azúcar en 4 semanas gracias a su fórmula única con bajo índice glicémico, carbohidratos de lenta digestión y m-inositol compuestoque ayuda a respaldar el metabolismo, los nivenes de glucosa y la sensibilidad a la insulina. Glucerna es nutrición especializada para personas con diabetes tipo 2 o hiperglicemia, es alta en proteina, sin azucares añadidos y fuente de 28 vitaminas y minerales. Glucerna actúa desde el primer día.
+Contiene 11 g de proteína y 8,8 g de fibra por porción para apoyar la saciedad, el metabolismo y la digestión.</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/jN6-t0Np34GU1RjqVgQm7nc5hB5mg3K04c7G9BTNg6bVYJkGKOqyRumsef0MPtjT14V_Q41Ie7O7k1agaW9cNS4pCZYp1ORZi7kW1oVzcEysejod=s360-rw</t>
+        </is>
+      </c>
       <c r="Q27" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/211200256-glucerna-16-kcal-frasco</t>
@@ -2097,7 +2590,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -2112,7 +2605,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Suero Rehidratante Pedialyte Max 60 Cloruro De Sodio 175.7 Mg Sabor Uva Frasco X 500 Ml</t>
+        </is>
+      </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
           <t>7501033957376</t>
@@ -2134,22 +2631,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
+        <v>144</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>ES UN MEDICAMENTO. NO EXCEDER SU CONSUMO. LEER INDICACIONES Y CONTRAINDICACIONES EN LA ETIQUETA. SI LOS SíNTOMAS PERSISTEN, CONSULTAR AL MÉDICO.</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/Yq2Aok4Fo_0fszI8lvm_IjRjKOpelIAanI7qEKUGF-NpIkia0PxSSWCtymAy9YK8sNWKVlTSyde1UvgjcOYkiY1tDkxe8hBaaUd8HzjjE9ZCEmf1=s360-rw</t>
+        </is>
+      </c>
       <c r="Q28" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/1036529-pedialyte-zinc-suero</t>
@@ -2157,7 +2670,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2685,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Suero Rehidratante Pedialyte Max 60 Cloruro De Sodio 175,7mg Sabor Fresa Frasco X 500 Ml</t>
+        </is>
+      </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
           <t>7501033961557</t>
@@ -2194,22 +2711,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
+        <v>144</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>ES UN MEDICAMENTO. NO EXCEDER SU CONSUMO. LEER INDICACIONES Y CONTRAINDICACIONES EN LA ETIQUETA. SI LOS SíNTOMAS PERSISTEN, CONSULTAR AL MÉDICO.</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/tXpTU8v4K-j20OgtfDhZyCzfUp3wjgt3sG9_JU11PV4J5YwNwbE10he6-3ixzgPq9dEVTYivoG8jXy-qzfUcVHX2f7lMGWdOfxAOvQsaImQQm8M=s360-rw</t>
+        </is>
+      </c>
       <c r="Q29" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/206650210-pedialyte-max-60-suero</t>
@@ -2217,7 +2750,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -2232,7 +2765,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Suero Rehidratante Pedialyte Max 60 Cloruro De Sodio 175,7 Mg Sabor Manzana Frasco X 500 Ml</t>
+        </is>
+      </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
           <t>7501033957369</t>
@@ -2254,22 +2791,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
+        <v>144</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>ES UN MEDICAMENTO. NO EXCEDER SU CONSUMO. LEER INDICACIONES Y CONTRAINDICACIONES EN LA ETIQUETA. SI LOS SíNTOMAS PERSISTEN, CONSULTAR AL MÉDICO.</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/OU2rmVTzxDP2iG_VZNc1Ar8COhn8odm8T2_Iu9nzEPHePKvD80G59f6y3zDKsfxF3tKsBzqajszSZzZBneew9Bway3bV-yEEohNiWtE0qB0_j7Vu=s360-rw</t>
+        </is>
+      </c>
       <c r="Q30" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/1036528-pedialyte-zinc-suero</t>
@@ -2277,7 +2830,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2845,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Suero Rehidratante Pedialyte Max 60 Cloruro De Sodio 176 Mg Sabor Coco Frasco X 500 Ml</t>
+        </is>
+      </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
           <t>7501033961540</t>
@@ -2314,22 +2871,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
+        <v>144</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>ES UN MEDICAMENTO. NO EXCEDER SU CONSUMO. LEER INDICACIONES Y CONTRAINDICACIONES EN LA ETIQUETA. SI LOS SíNTOMAS PERSISTEN, CONSULTAR AL MÉDICO.</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/j73sDFq6J1NlVPv-_tJ7kmYQZBIGukf0ZW2q3c2dm3MWjanoTTmw-Jz9tWV4mFGmOrYot_76w8eyOXZeiwQRrrZPp5iBHEHO32_Zl1L6TgNWuOILUA=s360-rw</t>
+        </is>
+      </c>
       <c r="Q31" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/206650201-pedialyte-max-60-suero</t>
@@ -2337,7 +2910,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -2352,7 +2925,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Suero Rehidratante Pedialyte Active Cloruro De Sodio 176.8 Mg Sabor Cereza Frasco X 500 Ml</t>
+        </is>
+      </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
           <t>7501033959967</t>
@@ -2374,22 +2951,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
+        <v>53</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>ESTE PRODUCTO REQUIERE FÓRMULA MÉDICA PARA SU COMPRA.</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/_h3Axzl-RNwHp7MwUgXJZo_5rI3cfAj_q8rpMBkac02RXBugUeWEpEsQdMH6FWGS6JQULrQVGP4bRcVNO2Jfg0ZQAvCauLZK8S3T8R3BIePIEzg=s360-rw</t>
+        </is>
+      </c>
       <c r="Q32" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/1051669-pedialyte-zinc-suero</t>
@@ -2397,7 +2990,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -2412,7 +3005,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Suero Rehidratante Pedialyte Active Cloruro De Sodio 176.6 Mg Sabor Fresa Frasco X 500 Ml</t>
+        </is>
+      </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
           <t>7501033957413</t>
@@ -2434,22 +3031,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
+        <v>144</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>ES UN MEDICAMENTO. NO EXCEDER SU CONSUMO. LEER INDICACIONES Y CONTRAINDICACIONES EN LA ETIQUETA. SI LOS SíNTOMAS PERSISTEN, CONSULTAR AL MÉDICO.</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/Wo54h-UGuwHXzZv9KHpB6sXG8Pmt6m5vYlPSOjwgrlT6M7fdSH60Ek_7I_2iU9U7dr-0dRmdnkoKzNRveNxnj7DK0REfo0iUg2LZPJnm1pcYbrS_=s360-rw</t>
+        </is>
+      </c>
       <c r="Q33" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/1036531-pedialyte-zinc-suero</t>
@@ -2457,7 +3070,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -2472,7 +3085,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Suero Rehidratante Pedialyte Active Glucosa Monohidratada 2.500 G Sabor Coco Frasco X 500ml</t>
+        </is>
+      </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
           <t>7501033959974</t>
@@ -2494,22 +3111,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
+        <v>144</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>ES UN MEDICAMENTO. NO EXCEDER SU CONSUMO. LEER INDICACIONES Y CONTRAINDICACIONES EN LA ETIQUETA. SI LOS SíNTOMAS PERSISTEN, CONSULTAR AL MÉDICO.</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/CQVGs7biX6r8Nr9OfVNL6zXl2s8ksdMUiaUbn6RcFWablrrfy8GkEnJRu1Gj-2ReAe80jdG1-6plNA19TMnX_nZEQsYvOB2FkO7w3BNx-WtgI9NX=s360-rw</t>
+        </is>
+      </c>
       <c r="Q34" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/1051671-pedialyte-zinc-suero</t>
@@ -2517,7 +3150,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -2532,7 +3165,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Suero Rehidratante Pedialyte Active Cloruro De Sodio 176.6 Mg Sabor Durazno Frasco X 500 Ml</t>
+        </is>
+      </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
           <t>7501033959981</t>
@@ -2554,22 +3191,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
+        <v>144</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>ES UN MEDICAMENTO. NO EXCEDER SU CONSUMO. LEER INDICACIONES Y CONTRAINDICACIONES EN LA ETIQUETA. SI LOS SíNTOMAS PERSISTEN, CONSULTAR AL MÉDICO.</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/ig2KuSWDAHg3p7ASrCEZbgkMYoCudN7KWfHqsDZ_jO_6XkO5H5RnlRFUDEU27CMuNReHj0ttZkjCcdsZR8tjasIqNd3TU5Zu3ORBkVph9LHolTU=s360-rw</t>
+        </is>
+      </c>
       <c r="Q35" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/1051672-pedialyte-zinc-suero</t>
@@ -2577,7 +3230,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -2592,7 +3245,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Fórmula Nutricional Pediasure Vainilla Niños 2-10 Años Tarro X 850 Gr</t>
+        </is>
+      </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
           <t>8886451012074</t>
@@ -2614,22 +3271,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
+        <v>467</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Complementa la nutrición de tu hijo con Pediasure, que contiene los 5 grupos de nutrientes especiales: Proteínas, Carbohidratos, Vitaminas, Minerales y Lípidos. Pediasure ahora está mejorado con fosfopéptidos de caseína, que ayudan a la absorción de nutrientes, reforzado con Vitamina K2 y Arginina. Resultados visibles a partir de las 8 semanas.
+Contiene arginina (500 mg) y vitamina K2 (4 mcg) que apoyan el desarrollo de huesos fuertes y el crecimiento saludable.</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/fg2M7bbuJ-_jx5Awys05fkBkvB6iw0OOOJUGfsUEhx4rV15KWW_54XQuc-3RGuTEvdmY81AEXjBaYidinj4qYkShc0EIJWBeE_Cv9xXg9_nPozH2=s360-rw</t>
+        </is>
+      </c>
       <c r="Q36" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/224700241-pediasure-peptigro-vainilla-lata-x-850-gr</t>
@@ -2637,7 +3311,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -2652,7 +3326,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Fórmula Nutricional Pediasure Sabor Vainilla Niños 2-10 Años Líquido Lata X 1600 Gr</t>
+        </is>
+      </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
           <t>8886451007049</t>
@@ -2674,22 +3352,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
+        <v>467</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Complementa la nutrición de tu hijo con Pediasure, que contiene los 5 grupos de nutrientes especiales: Proteínas, Carbohidratos, Vitaminas, Minerales y Lípidos. Pediasure ahora está mejorado con fosfopéptidos de caseína, que ayudan a la absorción de nutrientes, reforzado con Vitamina K2 y Arginina. Resultados visibles a partir de las 8 semanas.
+Contiene arginina (500 mg) y vitamina K2 (4 mcg) que apoyan el desarrollo de huesos fuertes y el crecimiento saludable.</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/Od0LMZNWmLbGTwfd1rciLwxjrzQuzkhGeD5YdWtjZdsoVHodBgw_793-exOcjsERWnoxt8mglGHpWUwtvDl2olNLQTfjgy0SmwL01nG6eu-P7SyIPQ=s360-rw</t>
+        </is>
+      </c>
       <c r="Q37" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/237700013-pediasure-ninos-sabor</t>
@@ -2697,7 +3392,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -2712,7 +3407,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Fórmula Nutricional Pediasure Sabor Vainilla Niños 2-10 Años Lata X 400 Gr</t>
+        </is>
+      </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
           <t>8886451012043</t>
@@ -2737,19 +3436,28 @@
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
+        <v>467</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Complementa la nutrición de tu hijo con Pediasure, que contiene los 5 grupos de nutrientes especiales: Proteínas, Carbohidratos, Vitaminas, Minerales y Lípidos. Pediasure ahora está mejorado con fosfopéptidos de caseína, que ayudan a la absorción de nutrientes, reforzado con Vitamina K2 y Arginina. Resultados visibles a partir de las 8 semanas.
+Contiene arginina (500 mg) y vitamina K2 (4 mcg) que apoyan el desarrollo de huesos fuertes y el crecimiento saludable.</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/5Y2oC_UHPBn2hoBGr4EWRLaj5KwBDrWzPEvGCJe7A0kvXsb3rX3j1XD1x6LvnNIQgKfASkkdX7hnqPyurJx2UbeM8qokuQ3-DwA_XALIpcaO3xIs1Q=s360-rw</t>
+        </is>
+      </c>
       <c r="Q38" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/224700250-pediasure-peptigro-vainilla-lata-x-400-gr</t>
@@ -2757,7 +3465,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -2772,7 +3480,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Fórmula Nutricional Pediasure Sabor Vainilla Niños 2-10 Años Liquido Botella X 220 Ml</t>
+        </is>
+      </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
           <t>8710428020185</t>
@@ -2794,22 +3506,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
+        <v>467</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Complementa la nutrición de tu hijo con Pediasure, que contiene los 5 grupos de nutrientes especiales: Proteínas, Carbohidratos, Vitaminas, Minerales y Lípidos. Pediasure ahora está mejorado con fosfopéptidos de caseína, que ayudan a la absorción de nutrientes, reforzado con Vitamina K2 y Arginina. Resultados visibles a partir de las 8 semanas.
+Contiene arginina (500 mg) y vitamina K2 (4 mcg) que apoyan el desarrollo de huesos fuertes y el crecimiento saludable.</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/q72Vyue8ZSNU8Hoc1Lf67zKIsWwXIMYYJCk1mHGr6o78JK7LTha0HunxO4YJQQMJPLecWmN_3OIyYadMX_sOy32avlU8Nm7rh1ZwdQ8bd5Dcr-e4=s360-rw</t>
+        </is>
+      </c>
       <c r="Q39" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/237800057-pediasure-rpb-sabor</t>
@@ -2817,7 +3546,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -2832,7 +3561,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Fórmula Nutricional Pediasure Sabor Fresa Niños 2-10 Años Líquido Frasco X 220 Ml</t>
+        </is>
+      </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
           <t>8710428020314</t>
@@ -2854,22 +3587,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
+        <v>467</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Complementa la nutrición de tu hijo con Pediasure, que contiene los 5 grupos de nutrientes especiales: Proteínas, Carbohidratos, Vitaminas, Minerales y Lípidos. Pediasure ahora está mejorado con fosfopéptidos de caseína, que ayudan a la absorción de nutrientes, reforzado con Vitamina K2 y Arginina. Resultados visibles a partir de las 8 semanas.
+Contiene arginina (500 mg) y vitamina K2 (4 mcg) que apoyan el desarrollo de huesos fuertes y el crecimiento saludable.</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/-L-Qn3oqLopbFCsN7h2sdbxF3upi7PIKFrFj6YYrfOvjnDv7P6mwz0YxIrTq9GJWRhn4mi-uukQoneuDjgjevbgLn5qlu46askbFBKPb26IS96z4=s360-rw</t>
+        </is>
+      </c>
       <c r="Q40" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/237850020-pediasure-rpb-sabor</t>
@@ -2877,7 +3627,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -2892,7 +3642,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Fórmula Nutricional Pediasure Sabor Fresa Niños 2-10 Años Lata X 850 Gr</t>
+        </is>
+      </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
           <t>8886451012036</t>
@@ -2917,19 +3671,28 @@
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
+        <v>467</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Complementa la nutrición de tu hijo con Pediasure, que contiene los 5 grupos de nutrientes especiales: Proteínas, Carbohidratos, Vitaminas, Minerales y Lípidos. Pediasure ahora está mejorado con fosfopéptidos de caseína, que ayudan a la absorción de nutrientes, reforzado con Vitamina K2 y Arginina. Resultados visibles a partir de las 8 semanas.
+Contiene arginina (500 mg) y vitamina K2 (4 mcg) que apoyan el desarrollo de huesos fuertes y el crecimiento saludable.</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/EDsIgJ2CTr-CPHl44TxKqufgu5_NOjeBnSIHSBlXgTqhngcEj4250p6_7P8VkjvWuxGeVQ-WtoP8IEmzZbDGCyKZjHOCJfz7w-Ywm1OftrYWI1YU_A=s360-rw</t>
+        </is>
+      </c>
       <c r="Q41" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/224650221-pediasure-peptigro-fresa-lata-x-850-gr</t>
@@ -2937,7 +3700,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -2952,7 +3715,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Complemento Nutricional Pediasure 10+ Sabor Vainilla Lata X 850 Gr</t>
+        </is>
+      </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
           <t>8710428021885</t>
@@ -2974,22 +3741,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
+        <v>426</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Apoya las necesidades nutricionales de tu adolescente con PediaSure 10+. Su fórmula especializada está diseñada para complementar la alimentación de adolescentes de 10 a 18 años que requieren apoyo nutricional especializado por una condición médica, déficit nutricional, riesgo nutricional o trastornos de la conducta alimentaria.
+Contiene arginina y vitamina K2, nutrientes que apoyan el crecimiento saludable de los huesos.</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/g06SnRkKIRNOpjTcGkO6P09bIQs8ygZPfVubAd8NSNIoz5F3eyjOR8wt3aJSYZ-UlzxWHB0UKh_ZJCTQGk8MuLXPKtJVcSR4_bOeJk85UaEftxo=s360-rw</t>
+        </is>
+      </c>
       <c r="Q42" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/235100241-pediasure-10-sabor-vainilla-lata-x-850-gr</t>
@@ -2997,7 +3781,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -3012,7 +3796,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Fórmula Nutricional Pediasure Fresa Niños 2-10 Años Tarro X 400 Gr</t>
+        </is>
+      </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
           <t>8886451012029</t>
@@ -3037,19 +3825,29 @@
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
+        <v>432</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Pediasure Peptigro Fresa 400gr Alimento con propósitos médicos especiales en polvo, polimérico, a base de maltodextrina, proteína, lípidos, vitaminas y minerales, para el manejo nutricional de nios de 2 a 13 años.
+Modo de uso:
+Para preparar una porción de 225mL servir en un vaso 190mL de agua fría o a temperatura ambiente y gradualmente añadir 5 meidas al ras aprox 48.6g de Pediasure Polvo. Agitar hasta disolver completamente.</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/-qHMEYy36DaMWko2_cxUs1Uxvr5_9w7oHDO-RCEVeUbEK49hEN3PSmVDCN7enb1_UE5ETIUHdLJFR57OZKwINc4bAzXSB7rn6zNgrUfvoUwonhwJ=s360-rw</t>
+        </is>
+      </c>
       <c r="Q43" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/224700233-pediasure-peptigro-fresa-lata-x-400-gr</t>
@@ -3057,7 +3855,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -3072,7 +3870,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Fórmula Nutricional Pediasure Peptigro Sabor Vainilla Liquido Caja X 6 Botellas 220 Ml C/u</t>
+        </is>
+      </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
           <t>7703186033130</t>
@@ -3094,22 +3896,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
+        <v>467</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Complementa la nutrición de tu hijo con Pediasure, que contiene los 5 grupos de nutrientes especiales: Proteínas, Carbohidratos, Vitaminas, Minerales y Lípidos. Pediasure ahora está mejorado con fosfopéptidos de caseína, que ayudan a la absorción de nutrientes, reforzado con Vitamina K2 y Arginina. Resultados visibles a partir de las 8 semanas.
+Contiene arginina (500 mg) y vitamina K2 (4 mcg) que apoyan el desarrollo de huesos fuertes y el crecimiento saludable.</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/0YpaVrbFWS5QP1OsMSiE6XFXJF-Dnj2QNk6HydqIteGEnri3OzA1zzrntMtvLQ8x3ngHAPWvMMfAnEv5mAIYIxWodi2GslAL-QhhHk3yzB8wuqcZ=s360-rw</t>
+        </is>
+      </c>
       <c r="Q44" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/239750129-pediasure-vainilla-rpb</t>
@@ -3117,7 +3936,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -3132,7 +3951,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Fórmula Nutricional Pediasure 10+ Sabor Vainilla Frasco X 220 Ml</t>
+        </is>
+      </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
           <t>8710428024039</t>
@@ -3154,22 +3977,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
+        <v>426</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Apoya las necesidades nutricionales de tu adolescente con PediaSure 10+. Su fórmula especializada está diseñada para complementar la alimentación de adolescentes de 10 a 18 años que requieren apoyo nutricional especializado por una condición médica, déficit nutricional, riesgo nutricional o trastornos de la conducta alimentaria.
+Contiene arginina y vitamina K2, nutrientes que apoyan el crecimiento saludable de los huesos.</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/HqAyW9qojBEUw1m6ojpkPUYaEy_nLsLIwWJUoku8AH-iZ5XzOb8jpQic_5Hvihw1AtksFgsk6ybgj4RD_tHOfnzjpIW008c0bINFMvBrikzTWOxU2g=s360-rw</t>
+        </is>
+      </c>
       <c r="Q45" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/236750203-pediasure-liquido-upage-10-sabor-vainilla-frasco-x-220-ml</t>
@@ -3177,7 +4017,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -3192,7 +4032,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Fórmula Infantil Etapa 1 Similac 5hmos 0-6 Meses Lata X 350 Gr</t>
+        </is>
+      </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
           <t>5099864016987</t>
@@ -3214,22 +4058,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
+        <v>554</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>La Fórmula Infantil Similac 1 con 5 HMO está diseñada para la alimentación de lactantes de 0 a 6 meses, cuando no es posible la lactancia materna o como complemento según indicación del profesional de salud.
+Su fórmula contiene 5 HMO (oligosacáridos estructuralmente similares a los presentes en la leche materna), además de nutrientes como hierro, DHA, luteína y nucleótidos, que participan en el desarrollo y crecimiento del bebé durante sus primeros meses de vida.
+Contiene hierro, nutriente importante para el crecimiento y desarrollo del lactante.</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/58NRiQs5cKJb7Gtp0PdIb_fVlYMtGS_6Gfg1APHNRn0t11i3KbpiGaLAyu7yytKRsABP8Ws8RXYaMEhO26pIX-CE-uxFi81CP7qlKuIJZLarGMQM=s360-rw</t>
+        </is>
+      </c>
       <c r="Q46" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/264700107-formula-infantil-similac-1-5-hmo-0-6-meses-lata-x-350-gr</t>
@@ -3237,7 +4099,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -3252,7 +4114,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Fórmula Infantil Etapa 1 Similac 5hmos 0-6 Meses Lata X 800 Gr</t>
+        </is>
+      </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
           <t>5099864016994</t>
@@ -3274,22 +4140,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
+        <v>447</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Esta fórmula infantil está desarrollada con base en nutrición científica para acompañar el desarrollo integral del bebé durante los primeros meses de vida. Su composición contribuye al apoyo de la salud intestinal y al proceso de maduración del sistema inmune.
+La presentación en lata de 800 gramos permite una preparación práctica dentro de la rutina diaria de alimentación del lactante, facilitando su almacenamiento y uso adecuado en el hogar.</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/jRfrj3NK_1nnb7KSu8jcNvlIg5j_vcq1xXpA3IG-C7m0I8om8YIeQP9-wUNDlmIKFLQqISIKDUM0V_G0d8Mh9fwpcu8Vth8goiHqKyzeoM9F43L_nQ=s360-rw</t>
+        </is>
+      </c>
       <c r="Q47" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/264700115-formula-infantil-similac-1-5-hmo-0-6-meses-lata-x-800-gr</t>
@@ -3297,7 +4180,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -3312,7 +4195,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Fórmula Infantil Etapa 1 Similac 5hmos 0-6 Meses Caja X 1400 Gr</t>
+        </is>
+      </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
           <t>7703186863072</t>
@@ -3334,22 +4221,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
+        <v>476</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Esta fórmula infantil está diseñada para acompañar la primera etapa de vida del bebé, brindando un apoyo nutricional durante el desarrollo inicial. Su composición busca integrarse dentro de la rutina de alimentación infantil, aportando nutrientes clave durante los primeros meses.
+La presentación en caja de 1400 gramos ofrece un formato familiar práctico para el uso continuo en el hogar, facilitando la preparación diaria dentro de la alimentación del lactante.
+Beneficios</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/vcI2HVoOsSB2hKfB1GXwlcwwSrPTopbg28mCazZo4NebSr3PZN6aua5rzg3Mzt2JN09N0bepZj2csh8glinDzFWh-x0xOtaQ0lapMHC8gkxnPXRM=s360-rw</t>
+        </is>
+      </c>
       <c r="Q48" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/264700086-formula-infantil-similac-1-5-hmo-0-6-meses-caja-x-1400-gr</t>
@@ -3357,7 +4262,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -3372,7 +4277,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Fórmula Infantil Etapa 1 Similac 5hmos 0-6 Meses Liquido X 59 Ml Caja X 8 Botellas</t>
+        </is>
+      </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
           <t>7703186497345</t>
@@ -3394,22 +4303,60 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
+        <v>2151</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Fórmula infantil líquida con hierro para lactantes de 0 a 6 meses con una combinación de grasas de fácil digestión, 5 HMOs (oligosacáridos), nucleótidos, DHA y luteína.
+Fórmula Infantil Similac 1 Líquida: Nutrición para los Primeros Meses
+La Fórmula Infantil Similac 1 Líquida está diseñada para lactantes de 0 a 6 meses. Su presentación en botellas individuales listas para servir ofrece una opción práctica para la alimentación del bebé, ideal para viajes o salidas.
+Presentación
+Formato: Líquido, listo para servir.
+Contenido del empaque: Caja con 8 botellas.
+Edad recomendada: Lactantes de 0 a 6 meses.
+País de producción: Estados Unidos.
+Registro sanitario: RSA-0018048-2022.
+Modo de Uso:
+Las instrucciones específicas de preparación, administración y conservación deben ser consultadas directamente en la etiqueta de cada botella y seguidas según la indicación del pediatra.
+Preguntas Frecuentes
+¿Cuál es el precio de la Fórmula Similac 1 Líquida?
+En Farmatodo se encuentra el precio para esta presentación de caja con 8 botellas. Consulte el valor actualizado directamente en la página del producto.
+¿Para qué edad está indicada?
+Esta fórmula está específicamente indicada para lactantes de 0 a 6 meses, según la descripción del producto.
+¿Qué contiene esta fórmula infantil?
+Según la información publicada, contiene hierro, una combinación de grasas de fácil digestión, 5 HMOs (oligosacáridos), nucleótidos, DHA y luteína.
+¿Dónde comprar la Fórmula Similac Líquida en Colombia?
+Este producto está disponible en Farmatodo. Puede adquirirse en las tiendas físicas o a través de la tienda online con servicio de envío a domicilio.
+Advertencia: La leche materna es el alimento ideal para el bebé. Consulte con su pediatra antes de utilizar fórmula infantil. Siga las instrucciones de la etiqueta para una preparación y uso seguros.
+Modo de uso:
+Presentación lista para servir, sin necesidad de medir polvo o preparar una mezcla con agua. Contiene una combinación de 5 HMO u oligosacáridos. Aporta hierro, nucleótidos, DHA y luteína como parte de su composición nutricional incluye una combinación de grasas de fácil digestión</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/s2RmDUhJIZyHO37qgGaO3MJgUcTMeCWtELczvxKbdc3fYK0-2vs5HdswhUAvqcoenzm_0-1JuqOHSOWOgUi2s9yQCnSP8qIilYNJQrBVxlUqdQQ=s360-rw</t>
+        </is>
+      </c>
       <c r="Q49" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/278600465-formula-infantil-similac</t>
@@ -3417,7 +4364,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -3432,7 +4379,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Fórmula Infantil Etapa 2 Similac 5hmos 6-12 Meses Lata X 1800 Gr</t>
+        </is>
+      </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
           <t>5099864017021</t>
@@ -3454,22 +4405,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
+        <v>723</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>La Fórmula Infantil Similac 2 5 HMO está diseñada como alimento de continuación para bebés a partir de los 6 meses. Su formulación incluye hierro, una combinación de grasas de fácil digestión, 5 HMOs (oligosacáridos inspirados en la leche materna), nucleótidos, DHA y luteína.
+Esta fórmula infantil acompaña las necesidades nutricionales del bebé durante la etapa de crecimiento, contribuyendo al desarrollo integral dentro de la rutina de alimentación diaria. Su formato pequeño de 350 gramos es práctico para viajes, salidas o para probar la tolerancia del bebé a la fórmula.
+La presentación en lata facilita su almacenamiento y preparación, ofreciendo una opción conveniente para complementar la alimentación infantil.</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/3nKu48reaGc1v0vZlfEHmOCzQ9g_QGhhZNn2kc0rOcsUQrbFr8AZgN__IXYFY1KeedraOKLLaFCZUn59OV_9Wc9pQ0mSDgnyDS0N1C4hcPJ38ws=s360-rw</t>
+        </is>
+      </c>
       <c r="Q50" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/264850076-formula-infantil-similac-2-6-meses-5hmo-lata-x-1800-gr</t>
@@ -3477,7 +4446,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -3492,7 +4461,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Fórmula Infantil Etapa 2 Similac 5hmos 6-12 Meses Caja X 1400 Gr</t>
+        </is>
+      </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
           <t>7703186502186</t>
@@ -3514,22 +4487,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
+        <v>735</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>La Fórmula Infantil Similac 2 5 HMO está diseñada como alimento de continuación para bebés a partir de los 6 meses. Su formulación incluye hierro, una combinación de grasas de fácil digestión, 5 HMOs (oligosacáridos inspirados en la leche materna), nucleótidos, DHA y luteína.
+Esta fórmula infantil acompaña las necesidades nutricionales del bebé durante la etapa de crecimiento, contribuyendo al desarrollo integral dentro de la rutina de alimentación diaria. Su formato pequeño de 350 gramos es práctico para viajes, salidas o para probar la tolerancia del bebé a la fórmula.
+La presentación en lata facilita su almacenamiento y preparación, ofreciendo una opción conveniente para complementar la alimentación infantil.
+Beneficios</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/dZAEcVTc_Sfsweyb0qCovtLWC4AVxSjTCc9iTe30ZsJDJhGKJF4vwnHxtXOd4CHqMfPzrRf8sMxY8a4qu8BIeg0UwowdpHqvXQPj_FnAL6x5LiCoVw=s360-rw</t>
+        </is>
+      </c>
       <c r="Q51" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/264850050-formula-infantil-similac-2-6-meses-5-hmo-caja-x-1400-gr</t>
@@ -3537,7 +4529,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -3552,7 +4544,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Fórmula Infantil Etapa 2 Similac 5hmos 6-12 Meses Lata X 350 Gr</t>
+        </is>
+      </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
           <t>5099864017007</t>
@@ -3574,22 +4570,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K52" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
+        <v>735</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>La Fórmula Infantil Similac 2 5 HMO está diseñada como alimento de continuación para bebés a partir de los 6 meses. Su formulación incluye hierro, una combinación de grasas de fácil digestión, 5 HMOs (oligosacáridos inspirados en la leche materna), nucleótidos, DHA y luteína.
+Esta fórmula infantil acompaña las necesidades nutricionales del bebé durante la etapa de crecimiento, contribuyendo al desarrollo integral dentro de la rutina de alimentación diaria. Su formato pequeño de 350 gramos es práctico para viajes, salidas o para probar la tolerancia del bebé a la fórmula.
+La presentación en lata facilita su almacenamiento y preparación, ofreciendo una opción conveniente para complementar la alimentación infantil.
+Beneficios</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/tCtKapYL8b3kxhXcoAiF2xRvpIa__mo5qkmKGznr9std5ZnD9fWiqF6d2O5eIclzxHVbE2ffcm3Ky5Kq1mzTIoiRLzat_6OR4OfpIDWKqVCyhk4T=s360-rw</t>
+        </is>
+      </c>
       <c r="Q52" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/264850092-formula-infantil-similac-2-6-meses-5-hmo-lata-x-350-gr</t>
@@ -3597,7 +4612,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -3612,7 +4627,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Fórmula Infantil Etapa 3 Similac 5hmos 12 Meses En Adelante Lata X 1800 Gr</t>
+        </is>
+      </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
           <t>5099864017229</t>
@@ -3634,22 +4653,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="K53" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
+        <v>652</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>A partir de los 2 años, los niños entran en una etapa llena de cambios, retos y mucho crecimiento. Similac 3 Kid está formulado para apoyar ese momento clave, combinando una mezcla única de grasas de fácil digestión con ingredientes como 5 HMOs, nucleótidos, DHA, luteína, hierro, calcio y vitamina D.
+Además, contiene probiótico y prebiótico, que junto con los 5 HMOs apoyan el buen funcionamiento del sistema inmune y gastrointestinal. Su fórmula está pensada para niños en crecimiento, ayudando a cubrir sus necesidades nutricionales mientras se preparan para nuevas etapas como el ingreso al jardín.
+Recomendado para niños a partir de los 2 años.</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/2rNnksy62WFuUZlf5Px9wwxBKg0hiGpFqoc93p_pczCiuupNDigTUFwht5JvESeKHaLz74ihJmT3__KV2a9RQvT-kvHQsfAsVlIuU2loXWTwVDJHOQ=s360-rw</t>
+        </is>
+      </c>
       <c r="Q53" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/264800087-formula-infantil-similac-3-5-hmo-lata-x-1800-gr</t>
@@ -3657,7 +4694,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -3672,7 +4709,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Fórmula Infantil Etapa 3 Similac 5hmos 12 Meses En Adelante Tarro X 800 Gr</t>
+        </is>
+      </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
           <t>5099864017212</t>
@@ -3694,22 +4735,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K54" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
+        <v>652</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>A partir de los 2 años, los niños entran en una etapa llena de cambios, retos y mucho crecimiento. Similac 3 Kid está formulado para apoyar ese momento clave, combinando una mezcla única de grasas de fácil digestión con ingredientes como 5 HMOs, nucleótidos, DHA, luteína, hierro, calcio y vitamina D.
+Además, contiene probiótico y prebiótico, que junto con los 5 HMOs apoyan el buen funcionamiento del sistema inmune y gastrointestinal. Su fórmula está pensada para niños en crecimiento, ayudando a cubrir sus necesidades nutricionales mientras se preparan para nuevas etapas como el ingreso al jardín.
+Recomendado para niños a partir de los 2 años.</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/dSYnjesHzUgfgrPy6e6ASwCV97_vkNzIwyElT1076zZ66f2qnJpDQmpSgSmWazA3pcpthIL-NSnbdws9mRigxJrgJrMbbyIGkVlyt8F7beaUO41c=s360-rw</t>
+        </is>
+      </c>
       <c r="Q54" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/264850113-formula-infantil-similac-3-5-hmo-lata-x-800-gr</t>
@@ -3717,7 +4776,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -3732,7 +4791,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Fórmula Infantil Etapa 3 Similac 5hmos 12 Meses En Adelante Lata X 350 Gr</t>
+        </is>
+      </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
           <t>5099864017205</t>
@@ -3754,22 +4817,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
+        <v>652</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>A partir de los 2 años, los niños entran en una etapa llena de cambios, retos y mucho crecimiento. Similac 3 Kid está formulado para apoyar ese momento clave, combinando una mezcla única de grasas de fácil digestión con ingredientes como 5 HMOs, nucleótidos, DHA, luteína, hierro, calcio y vitamina D.
+Además, contiene probiótico y prebiótico, que junto con los 5 HMOs apoyan el buen funcionamiento del sistema inmune y gastrointestinal. Su fórmula está pensada para niños en crecimiento, ayudando a cubrir sus necesidades nutricionales mientras se preparan para nuevas etapas como el ingreso al jardín.
+Recomendado para niños a partir de los 2 años.</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/9dtSiGQeoBvHHAAtl7vTZz1FKWc6vhQsPuI7mNvOj4KQNdIKEk91yCTb62FIVvGtpa5bqluAv_kVg36n9NtNxKMfVMxg3bBGIlgpc_KltGd7cdsV=s360-rw</t>
+        </is>
+      </c>
       <c r="Q55" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/264800095-formula-infantil-similac-3-5-hmo-lata-x-350-gr</t>
@@ -3777,7 +4858,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -3792,7 +4873,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Fórmula Similac Mamá Para Madres Gestantes Y Lactantes Lata X 400 Gr</t>
+        </is>
+      </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
           <t>7703186029508</t>
@@ -3814,22 +4899,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
+        <v>464</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Similac Mamá en polvo (400 gr) es un complemento nutricional especializado. Alimento a base de leche en polvo descremada, con vitaminas y minerales para mujeres embarazadas y en periodo de lactancia. Enriquecido con DHA, ácido fólico, hierro, calcio y prebióticos, apoya la salud materna y el óptimo desarrollo fetal y del lactante.
+Puede utilizarse durante la lactancia como parte de una alimentación equilibrada y de un programa de apoyo a la lactancia materna.</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/Da107bf_6lALPY1_N-VHZwClOt07aTAl8EFz1WNErozhMpwjAqEUuqXhJhK_0K8msFrjj1CfjyYK2avp9vtTgLrYsF7qZqh0aLXGO4CaMwWSHvFS=s360-rw</t>
+        </is>
+      </c>
       <c r="Q56" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/1043377-leche-en-polvo-similac</t>
@@ -3837,7 +4939,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -3852,7 +4954,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Fórmula Infantil Especializada Similac Neosure Prematuros 0-12 Meses Lata X 370 Gr</t>
+        </is>
+      </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
           <t>8427030003658</t>
@@ -3874,22 +4980,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
+        <v>153</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Uso oral. Fórmula infantil con ácido araquidónico, ácido docosahexaenoico y nucleótidos para bebes prematuros y/o con bajo peso al nacer de 0 a 12 meses.</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/50QWFHUpeIXibHlK0m1buSE2FvF43opN114fk1HitAo89LzRiLFh1tBaEaZw5JZSvmFmtBGltOnyXKgRpdNf7rHoCYezDts39hAChgnTL63y-RSRQg=s360-rw</t>
+        </is>
+      </c>
       <c r="Q57" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/1037373-formula-infantil-similac-prematuros</t>
@@ -3897,7 +5019,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -3912,7 +5034,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Fórmula Infantil Especializada Similac Rice Proteína De Arroz 0-36 Meses Lata X 400 Gr</t>
+        </is>
+      </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
           <t>5099864017236</t>
@@ -3934,22 +5060,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K58" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
+        <v>833</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>La Fórmula Infantil Similac Rice está desarrollada para la alimentación de lactantes desde el nacimiento hasta los 12 meses. Su formulación está basada en proteína de arroz extensamente hidrolizada, ofreciendo una alternativa nutricional para bebés con sospecha de alergia a la proteína de leche de vaca.
+Esta fórmula especializada incluye hierro, prebiótico HMO 2-FL, nucleótidos, DHA y ARA, nutrientes que contribuyen al adecuado crecimiento y desarrollo del bebé durante el primer año de vida. Su composición nutricional permite integrarse dentro de la rutina de alimentación infantil como una opción diseñada para necesidades específicas.
+La presentación en lata de 400 gramos facilita su almacenamiento y preparación diaria dentro del hogar.
+Alternativa para lactantes con sospecha de alergia a la proteína de leche de vaca.</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/CzMf_SXiAuOj3jwxUcFp3HXcbKhtUYb7e_SONlyY2psEi1oHGhwaFPhxkWOkkii_-JdJHhDnkXD7fvwmRywk8As7x5peMFVBbAOzk7p5pPfiCvAf=s360-rw</t>
+        </is>
+      </c>
       <c r="Q58" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/263800018-formula-infantil-similac-rice-0-12-meses-x-400-gr</t>
@@ -3957,7 +5102,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -3972,7 +5117,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Fórmula Infantil Similac Sensitive Sl Eye Q Sin Lactosa 0-12 Meses X 375 Gr</t>
+        </is>
+      </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
           <t>8427030003238</t>
@@ -3994,22 +5143,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="K59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
+        <v>396</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Similac Sensitive Sin Lactosa (375 gr) es una fórmula infantil especializada a base de leche, diseñada para lactantes de 0 a 12 meses con intolerancia a la lactosa, gases, cólicos o molestias digestivas asociadas. Brinda una nutrición completa para el crecimiento y desarrollo integral del bebé mientras favorece su confort estomacal.
+Fórmula sin lactosa para necesidades especiales de nutrición</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/-hXuQwZUX1Vgo_SrdMdYwP0uRxu-Yw69_DqPI-1qGNvf4hCA6XGmvOIOUckSoBpzTrcrlOyJA7AWbmTdMLf8XL3zBa8NqO96gp9qkXGiiEacr-9x=s360-rw</t>
+        </is>
+      </c>
       <c r="Q59" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/1013041-formula-infantil-similac</t>
@@ -4017,7 +5183,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -4032,7 +5198,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Fórmula Infantil Etapa 2 Similac Total Comfort 12-36 Meses Lata X 820 Gr</t>
+        </is>
+      </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
           <t>8427030008820</t>
@@ -4054,22 +5224,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
+        <v>294</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Alimento lácteo, bajo en lactosa, con proteína parcialmente hidrolizada, mezcla de grasas de fácil digestión, prebiótico HMO 2'-FL, DHA y luteína para niños de 1 a 3 años. Alimento de continuación para bebés con digestión sensible. Proteína hidrolizada que reduce gases, llanto y estreñimiento.</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/M2IFLxhoGwXPLZVpAlgyACVJSqoD9TUwqeAelQgld_GevjhvdHLome1mxdz9LM45lhDJ5jspOK8ZsNddrz41S7a9dgMIK2JWiUAxFlrNYzEqa0Ce=s360-rw</t>
+        </is>
+      </c>
       <c r="Q60" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/293350505-formula-infantil-similac-total-comfort-2-prosensitive-lata-x-820-gr</t>
@@ -4077,7 +5263,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -4092,7 +5278,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Fórmula Infantil Etapa 1 Similac Total Comfort 0-12 Meses Polvo Caja X 1400 Gr</t>
+        </is>
+      </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
           <t>7703186032355</t>
@@ -4114,22 +5304,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="K61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
+        <v>594</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Similac Total Comfort 1 5HMO es una formula Infantil con Hierro, Proteina Parcialmente Hidrolizada, Grasas De Facil Digestión, prebioticos, 5hmos, Nucleotidos, Dha Y Luteina, Baja En Lactosa, libre de oleina de palmapara Lactantes De 0 A 12 Meses que requieren apoyo nutricional para una mejor digestión y tolerancia. Características pensadas para acompañar el bienestar digestivo de tu pequeño durante una etapa importante de crecimiento y desarrollo.
+Similac Total Comfort Kid está diseñada para apoyar una fácil digestión con menos gases y diarrea.
+Gracias a su mezcla única de nutrientes:</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/Zj0rfIQVWHZ-OKNF08UvaSfj8WegRKnBUSztFg3wuBwtNBfEIjPxElusc03X-L3eGpVMPQqBUspcRH49N5SI_AhSbbhX277GFrKaq-Vif-JHCqYr=s360-rw</t>
+        </is>
+      </c>
       <c r="Q61" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/1053211-formula-infantil-similac-etapa-1</t>
@@ -4137,7 +5345,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -4152,7 +5360,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Fórmula Infantil Etapa 1 Similac Total Comfort 0-12 Meses Lata X 800 Gr</t>
+        </is>
+      </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
           <t>8427030009285</t>
@@ -4177,19 +5389,29 @@
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
+        <v>594</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Similac Total Comfort 1 5HMO es una formula Infantil con Hierro, Proteina Parcialmente Hidrolizada, Grasas De Facil Digestión, prebioticos, 5hmos, Nucleotidos, Dha Y Luteina, Baja En Lactosa, libre de oleina de palmapara Lactantes De 0 A 12 Meses que requieren apoyo nutricional para una mejor digestión y tolerancia. Características pensadas para acompañar el bienestar digestivo de tu pequeño durante una etapa importante de crecimiento y desarrollo.
+Similac Total Comfort Kid está diseñada para apoyar una fácil digestión con menos gases y diarrea.
+Gracias a su mezcla única de nutrientes:</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/aDnHhSDwCWnA155fJQ8aws1j55qZZ7RWQrV_lR3fM8jh-ShdWpZqy_hM_mRv-_iH6dXljC4zapTC1YFKBCKuERcbPMlFuAkLV6Yo7Lbswvdvc0X6jA=s360-rw</t>
+        </is>
+      </c>
       <c r="Q62" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/244800207-formula-infantil-similac-total-comfort-5hmos-etapa-1-x-800-gr</t>
@@ -4197,7 +5419,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
@@ -4212,7 +5434,11 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr"/>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Fórmula Infantil Etapa 1 Similac Total Comfort 0-12 Meses Lata X 350 Gr</t>
+        </is>
+      </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
           <t>8427030009278</t>
@@ -4234,22 +5460,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
-      </c>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
+        <v>594</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Similac Total Comfort 1 5HMO es una formula Infantil con Hierro, Proteina Parcialmente Hidrolizada, Grasas De Facil Digestión, prebioticos, 5hmos, Nucleotidos, Dha Y Luteina, Baja En Lactosa, libre de oleina de palmapara Lactantes De 0 A 12 Meses que requieren apoyo nutricional para una mejor digestión y tolerancia. Características pensadas para acompañar el bienestar digestivo de tu pequeño durante una etapa importante de crecimiento y desarrollo.
+Similac Total Comfort Kid está diseñada para apoyar una fácil digestión con menos gases y diarrea.
+Gracias a su mezcla única de nutrientes:</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>https://product-images.farmatodo.com/PHhfrejrnauq_8sqtyHC6V-mcu5fHDbbbVTpzSvfDofbnydZtAQuwbHIETMGLFn083v0c-0MzfrUpHTFcZF1GNaMAoJLtHmduiBF_kVs-hOqq9I=s360-rw</t>
+        </is>
+      </c>
       <c r="Q63" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/244750203-formula-infantil-similac-total-comfort-5hmos-etapa-1-x-350-gr</t>
@@ -4257,7 +5501,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
